--- a/BWI/bestwine_output/bestwine_Antigua and Barbuda.xlsx
+++ b/BWI/bestwine_output/bestwine_Antigua and Barbuda.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,8 +29,11 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
+    <font>
+      <color rgb="00276221"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -40,6 +43,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="004F1A2A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
   </fills>
@@ -55,11 +63,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,8 +434,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <dimension ref="A1:AA10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
     <col width="25" customWidth="1" min="2" max="2"/>
@@ -630,7 +639,6 @@
           <t>Epicurean Drive</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
           <t>http://www.epicureanantigua.com</t>
@@ -676,7 +684,6 @@
           <t>B314/08</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
           <t>https://www.facebook.com/epicureanantigua</t>
@@ -687,13 +694,6 @@
           <t>https://www.instagram.com/epicureanantigua</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -731,8 +731,6 @@
           <t>Nugent Avenue</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
           <t>Distributor, Retailer</t>
@@ -773,7 +771,6 @@
           <t>C405</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr">
         <is>
           <t>https://www.facebook.com/QuinFarara/</t>
@@ -784,8 +781,6 @@
           <t>https://www.instagram.com/quinfarara268</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr">
         <is>
           <t>Paul Farara</t>
@@ -796,8 +791,6 @@
           <t>Owner</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr"/>
-      <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/paul-farara-0a069012</t>
@@ -840,7 +833,6 @@
           <t>Friars Hill Road</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
           <t>https://premiercru.biz</t>
@@ -901,8 +893,6 @@
           <t>https://www.instagram.com/premiercruretailstores/</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr">
         <is>
           <t>Jason Gilead</t>
@@ -913,8 +903,6 @@
           <t>Managing Director</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/jason-gilead-8bb7b0184/</t>
@@ -957,7 +945,6 @@
           <t>Friars Hill Road</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
           <t>https://premiercru.biz</t>
@@ -1018,8 +1005,6 @@
           <t>https://www.instagram.com/premiercruretailstores/</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr">
         <is>
           <t>Anthony Bento</t>
@@ -1030,8 +1015,6 @@
           <t>Managing Director</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr"/>
-      <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/a-anthony-bento-4828634/</t>
@@ -1074,7 +1057,6 @@
           <t>Friars Hill Road</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
           <t>https://premiercru.biz</t>
@@ -1135,8 +1117,6 @@
           <t>https://www.instagram.com/premiercruretailstores/</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr">
         <is>
           <t>Placido Sariol</t>
@@ -1147,8 +1127,6 @@
           <t>Senior Wine Representative/ Sales Representative</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr"/>
-      <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/placido-sariol-251252b8/</t>
@@ -1191,7 +1169,6 @@
           <t>Redcliffe Quay</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
           <t>https://ccwinehouse.com</t>
@@ -1237,15 +1214,11 @@
           <t>B368/08</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr">
         <is>
           <t>https://www.facebook.com/ccwinehouseantigua</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr"/>
       <c r="W7" t="inlineStr">
         <is>
           <t>Claudine Vierstraete</t>
@@ -1256,8 +1229,6 @@
           <t>Director</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr"/>
-      <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/claudine-vierstraete-07506825</t>
@@ -1300,8 +1271,6 @@
           <t>Silver Leaf Plaza, Weatherall's Road</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
           <t>Retailer</t>
@@ -1312,8 +1281,6 @@
           <t>Wine, Spirits, Sparkling Wine</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>thecorkandbasket@brydensantigua.com</t>
@@ -1334,7 +1301,6 @@
           <t>B1028/16</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr">
         <is>
           <t>https://www.facebook.com/thecorkandbasket/</t>
@@ -1345,8 +1311,6 @@
           <t>https://www.instagram.com/thecorkandbasket/</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr"/>
       <c r="W8" t="inlineStr">
         <is>
           <t>Kamlesh Vaswani</t>
@@ -1357,11 +1321,227 @@
           <t>Sales &amp; Marketing Representative</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr"/>
-      <c r="Z8" t="inlineStr"/>
       <c r="AA8" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/kamlesh-vaswani-71aa16168/</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Premier Retail Stores Ltd</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Premier Retail Stores Ltd</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>50175</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Antigua and Barbuda</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Saint John's</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Saint John</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>Friars Hill Road</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr"/>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>https://premiercru.biz</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="inlineStr"/>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>jason.gilead@premierbev.biz</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>+1 268-480-3200</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>10882403</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/premier-beverages-limited/</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/PremierCruRetailStores/</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/premiercruretailstores/</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr"/>
+      <c r="V9" s="2" t="inlineStr"/>
+      <c r="W9" s="2" t="inlineStr">
+        <is>
+          <t>Placido Sariol</t>
+        </is>
+      </c>
+      <c r="X9" s="2" t="inlineStr">
+        <is>
+          <t>Senior Wine Representative/ Sales Representative</t>
+        </is>
+      </c>
+      <c r="Y9" s="2" t="inlineStr"/>
+      <c r="Z9" s="2" t="inlineStr"/>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/placido-sariol-251252b8/</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Premier Retail Stores Ltd</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Premier Retail Stores Ltd</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>50175</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Antigua and Barbuda</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Saint John's</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Saint John</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>Friars Hill Road</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr"/>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>https://premiercru.biz</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>jason.gilead@premierbev.biz</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>+1 268-480-3200</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>10882403</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/premier-beverages-limited/</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/PremierCruRetailStores/</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/premiercruretailstores/</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr"/>
+      <c r="V10" s="2" t="inlineStr"/>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
+          <t>Jason Gilead</t>
+        </is>
+      </c>
+      <c r="X10" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y10" s="2" t="inlineStr"/>
+      <c r="Z10" s="2" t="inlineStr"/>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/jason-gilead-8bb7b0184/</t>
         </is>
       </c>
     </row>

--- a/BWI/bestwine_output/bestwine_Antigua and Barbuda.xlsx
+++ b/BWI/bestwine_output/bestwine_Antigua and Barbuda.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA10"/>
+  <dimension ref="A1:AA12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1545,6 +1545,224 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Premier Retail Stores Ltd</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Premier Retail Stores Ltd</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>50175</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Antigua and Barbuda</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Saint John's</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Saint John</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>Friars Hill Road</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr"/>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>https://premiercru.biz</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>jason.gilead@premierbev.biz</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>+1 268-480-3200</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>10882403</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/premier-beverages-limited/</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/PremierCruRetailStores/</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/premiercruretailstores/</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr"/>
+      <c r="V11" s="2" t="inlineStr"/>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
+          <t>Placido Sariol</t>
+        </is>
+      </c>
+      <c r="X11" s="2" t="inlineStr">
+        <is>
+          <t>Senior Wine Representative/ Sales Representative</t>
+        </is>
+      </c>
+      <c r="Y11" s="2" t="inlineStr"/>
+      <c r="Z11" s="2" t="inlineStr"/>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/placido-sariol-251252b8/</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Premier Retail Stores Ltd</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Premier Retail Stores Ltd</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>50175</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Antigua and Barbuda</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Saint John's</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Saint John</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>Friars Hill Road</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr"/>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>https://premiercru.biz</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>jason.gilead@premierbev.biz</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>+1 268-480-3200</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>10882403</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/premier-beverages-limited/</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/PremierCruRetailStores/</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/premiercruretailstores/</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr"/>
+      <c r="V12" s="2" t="inlineStr"/>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
+          <t>Jason Gilead</t>
+        </is>
+      </c>
+      <c r="X12" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y12" s="2" t="inlineStr"/>
+      <c r="Z12" s="2" t="inlineStr"/>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/jason-gilead-8bb7b0184/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Antigua and Barbuda.xlsx
+++ b/BWI/bestwine_output/bestwine_Antigua and Barbuda.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA12"/>
+  <dimension ref="A1:AA14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1763,6 +1763,224 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Premier Retail Stores Ltd</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Premier Retail Stores Ltd</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>50175</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Antigua and Barbuda</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Saint John's</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Saint John</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>Friars Hill Road</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr"/>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>https://premiercru.biz</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>jason.gilead@premierbev.biz</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>+1 268-480-3200</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>10882403</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/premier-beverages-limited/</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/PremierCruRetailStores/</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/premiercruretailstores/</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr"/>
+      <c r="V13" s="2" t="inlineStr"/>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
+          <t>Placido Sariol</t>
+        </is>
+      </c>
+      <c r="X13" s="2" t="inlineStr">
+        <is>
+          <t>Senior Wine Representative/ Sales Representative</t>
+        </is>
+      </c>
+      <c r="Y13" s="2" t="inlineStr"/>
+      <c r="Z13" s="2" t="inlineStr"/>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/placido-sariol-251252b8/</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Premier Retail Stores Ltd</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Premier Retail Stores Ltd</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>50175</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Antigua and Barbuda</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Saint John's</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Saint John</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>Friars Hill Road</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr"/>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>https://premiercru.biz</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>jason.gilead@premierbev.biz</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>+1 268-480-3200</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>10882403</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/premier-beverages-limited/</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/PremierCruRetailStores/</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/premiercruretailstores/</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr"/>
+      <c r="V14" s="2" t="inlineStr"/>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
+          <t>Jason Gilead</t>
+        </is>
+      </c>
+      <c r="X14" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y14" s="2" t="inlineStr"/>
+      <c r="Z14" s="2" t="inlineStr"/>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/jason-gilead-8bb7b0184/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Antigua and Barbuda.xlsx
+++ b/BWI/bestwine_output/bestwine_Antigua and Barbuda.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA14"/>
+  <dimension ref="A1:AA16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1981,6 +1981,224 @@
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Premier Retail Stores Ltd</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Premier Retail Stores Ltd</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>50175</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Antigua and Barbuda</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Saint John's</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Saint John</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>Friars Hill Road</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr"/>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>https://premiercru.biz</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>jason.gilead@premierbev.biz</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>+1 268-480-3200</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr">
+        <is>
+          <t>10882403</t>
+        </is>
+      </c>
+      <c r="R15" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/premier-beverages-limited/</t>
+        </is>
+      </c>
+      <c r="S15" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/PremierCruRetailStores/</t>
+        </is>
+      </c>
+      <c r="T15" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/premiercruretailstores/</t>
+        </is>
+      </c>
+      <c r="U15" s="2" t="inlineStr"/>
+      <c r="V15" s="2" t="inlineStr"/>
+      <c r="W15" s="2" t="inlineStr">
+        <is>
+          <t>Jason Gilead</t>
+        </is>
+      </c>
+      <c r="X15" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y15" s="2" t="inlineStr"/>
+      <c r="Z15" s="2" t="inlineStr"/>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/jason-gilead-8bb7b0184/</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Premier Retail Stores Ltd</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Premier Retail Stores Ltd</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>50175</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Antigua and Barbuda</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Saint John's</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Saint John</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>Friars Hill Road</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr"/>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>https://premiercru.biz</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>jason.gilead@premierbev.biz</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>+1 268-480-3200</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>10882403</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/premier-beverages-limited/</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/PremierCruRetailStores/</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/premiercruretailstores/</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr"/>
+      <c r="V16" s="2" t="inlineStr"/>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
+          <t>Placido Sariol</t>
+        </is>
+      </c>
+      <c r="X16" s="2" t="inlineStr">
+        <is>
+          <t>Senior Wine Representative/ Sales Representative</t>
+        </is>
+      </c>
+      <c r="Y16" s="2" t="inlineStr"/>
+      <c r="Z16" s="2" t="inlineStr"/>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/placido-sariol-251252b8/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
